--- a/Result/profitability/4120.xlsx
+++ b/Result/profitability/4120.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8462500000000001</v>
+        <v>-1.12625</v>
       </c>
       <c r="N2" t="n">
-        <v>47.18875</v>
+        <v>47.36125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.82</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.76</v>
+        <v>-0.82875</v>
       </c>
       <c r="N3" t="n">
-        <v>46.435</v>
+        <v>46.54875000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.96</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.445</v>
+        <v>-0.4874999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>45.72</v>
+        <v>45.56875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.87</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.115</v>
+        <v>-0.3125</v>
       </c>
       <c r="N5" t="n">
-        <v>44.52625</v>
+        <v>44.09375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.135</v>
+        <v>0.05750000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>43.63625</v>
+        <v>43.30625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.44625</v>
+        <v>0.5275</v>
       </c>
       <c r="N7" t="n">
-        <v>42.775</v>
+        <v>42.8125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8462500000000001</v>
+        <v>0.61875</v>
       </c>
       <c r="N8" t="n">
-        <v>42.0425</v>
+        <v>41.41375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>0.78</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9825</v>
+        <v>0.9824999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>40.8425</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4120</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1189</v>
+      </c>
+      <c r="D75" t="n">
+        <v>631</v>
+      </c>
+      <c r="E75" t="n">
+        <v>558</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-10.54%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>52</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-73</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-183</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.2975</v>
+      </c>
+      <c r="N75" t="n">
+        <v>48.18875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="X75" t="n">
+        <v>6.275862068965517</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.030000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09673076923076929</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.981132075471698</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.460000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06860995439222684</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
